--- a/python/outputs/tables/result_summary_for_paper.xlsx
+++ b/python/outputs/tables/result_summary_for_paper.xlsx
@@ -731,16 +731,16 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="G2" t="n">
-        <v>27.85930565744964</v>
+        <v>28.10445952436107</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6041326207832896</v>
+        <v>0.6067116918666002</v>
       </c>
       <c r="I2" t="n">
-        <v>63.28017600709892</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11.93637499279126</v>
+        <v>12.19293112289475</v>
       </c>
       <c r="L2" t="n">
-        <v>1976.48401826484</v>
+        <v>1988.094130375551</v>
       </c>
       <c r="M2" t="n">
-        <v>3271.606184255082</v>
+        <v>3276.835038828756</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         <v>56.13098118801251</v>
       </c>
       <c r="G3" t="n">
-        <v>29.44826858247547</v>
+        <v>29.78877634891348</v>
       </c>
       <c r="H3" t="n">
         <v>9.644557091626965</v>
       </c>
       <c r="I3" t="n">
-        <v>64.67835877380573</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -838,13 +838,13 @@
         <v>56.45064246517819</v>
       </c>
       <c r="G4" t="n">
-        <v>29.46159607805437</v>
+        <v>29.80209788084358</v>
       </c>
       <c r="H4" t="n">
         <v>9.964218368792643</v>
       </c>
       <c r="I4" t="n">
-        <v>64.67835877380573</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -890,13 +890,13 @@
         <v>56.45064246517819</v>
       </c>
       <c r="G5" t="n">
-        <v>29.46159607805437</v>
+        <v>29.80209788084358</v>
       </c>
       <c r="H5" t="n">
         <v>9.964218368792643</v>
       </c>
       <c r="I5" t="n">
-        <v>64.67835877380573</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         <v>55.48778562930227</v>
       </c>
       <c r="G6" t="n">
-        <v>29.41749755707069</v>
+        <v>29.75799935985989</v>
       </c>
       <c r="H6" t="n">
         <v>9.001361532916725</v>
       </c>
       <c r="I6" t="n">
-        <v>64.67835877380573</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1306,34 +1306,34 @@
         <v>41.53844690354869</v>
       </c>
       <c r="D2" t="n">
-        <v>173529.4486494036</v>
+        <v>173541.6895787274</v>
       </c>
       <c r="E2" t="n">
         <v>117339.7881594676</v>
       </c>
       <c r="F2" t="n">
-        <v>4177.562272665971</v>
+        <v>4177.856961809073</v>
       </c>
       <c r="G2" t="n">
         <v>2824.847747243124</v>
       </c>
       <c r="H2" t="n">
-        <v>1352.714525422847</v>
+        <v>1353.009214565949</v>
       </c>
       <c r="I2" t="n">
-        <v>56189.66048993601</v>
+        <v>56201.90141925981</v>
       </c>
       <c r="J2" t="n">
         <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>2602941.729741055</v>
+        <v>2603125.343680912</v>
       </c>
       <c r="L2" t="n">
         <v>1760096.822392014</v>
       </c>
       <c r="M2" t="n">
-        <v>842844.9073490401</v>
+        <v>843028.5212888971</v>
       </c>
     </row>
     <row r="3">
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.48301548127506</v>
+        <v>32.0372530120482</v>
       </c>
       <c r="C3" t="n">
-        <v>31.48301548127506</v>
+        <v>32.0372530120482</v>
       </c>
       <c r="D3" t="n">
-        <v>125673.2002605049</v>
+        <v>126520.8141909006</v>
       </c>
       <c r="E3" t="n">
-        <v>114187.5234639879</v>
+        <v>118009.1482726357</v>
       </c>
       <c r="F3" t="n">
-        <v>3991.7777360066</v>
+        <v>3949.177981748938</v>
       </c>
       <c r="G3" t="n">
-        <v>3626.956367375368</v>
+        <v>3683.497715245942</v>
       </c>
       <c r="H3" t="n">
-        <v>364.8213686312315</v>
+        <v>265.6802665029959</v>
       </c>
       <c r="I3" t="n">
-        <v>11485.67679651701</v>
+        <v>8511.665918264873</v>
       </c>
       <c r="J3" t="n">
         <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>1885098.003907573</v>
+        <v>1897812.212863509</v>
       </c>
       <c r="L3" t="n">
-        <v>1712812.851959818</v>
+        <v>1770137.224089536</v>
       </c>
       <c r="M3" t="n">
-        <v>172285.1519477552</v>
+        <v>127674.9887739731</v>
       </c>
     </row>
     <row r="4">
@@ -1386,40 +1386,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.8579184230318</v>
+        <v>20.59317108433735</v>
       </c>
       <c r="C4" t="n">
-        <v>19.8579184230318</v>
+        <v>20.59317108433735</v>
       </c>
       <c r="D4" t="n">
-        <v>86395.25382609818</v>
+        <v>87519.70022945481</v>
       </c>
       <c r="E4" t="n">
-        <v>80002.47979765691</v>
+        <v>84711.18489118994</v>
       </c>
       <c r="F4" t="n">
-        <v>4350.670195416576</v>
+        <v>4249.937995028852</v>
       </c>
       <c r="G4" t="n">
-        <v>4028.744508531553</v>
+        <v>4113.55708862241</v>
       </c>
       <c r="H4" t="n">
-        <v>321.9256868850234</v>
+        <v>136.3809064064426</v>
       </c>
       <c r="I4" t="n">
-        <v>6392.774028441272</v>
+        <v>2808.515338264871</v>
       </c>
       <c r="J4" t="n">
         <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>1295928.807391473</v>
+        <v>1312795.503441822</v>
       </c>
       <c r="L4" t="n">
-        <v>1200037.196964854</v>
+        <v>1270667.773367849</v>
       </c>
       <c r="M4" t="n">
-        <v>95891.61042661908</v>
+        <v>42127.73007397307</v>
       </c>
     </row>
     <row r="5">
@@ -1429,40 +1429,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.2036679576071</v>
+        <v>16.00987951807229</v>
       </c>
       <c r="C5" t="n">
-        <v>15.2036679576071</v>
+        <v>16.00987951807229</v>
       </c>
       <c r="D5" t="n">
-        <v>70886.53144764202</v>
+        <v>72119.49766078012</v>
       </c>
       <c r="E5" t="n">
-        <v>66724.36996698413</v>
+        <v>72088.23414251524</v>
       </c>
       <c r="F5" t="n">
-        <v>4662.462482428405</v>
+        <v>4504.687095200817</v>
       </c>
       <c r="G5" t="n">
-        <v>4388.702131159002</v>
+        <v>4502.734331082286</v>
       </c>
       <c r="H5" t="n">
-        <v>273.7603512694022</v>
+        <v>1.952764118530467</v>
       </c>
       <c r="I5" t="n">
-        <v>4162.161480657887</v>
+        <v>31.26351826488099</v>
       </c>
       <c r="J5" t="n">
         <v>15</v>
       </c>
       <c r="K5" t="n">
-        <v>1063297.97171463</v>
+        <v>1081792.464911702</v>
       </c>
       <c r="L5" t="n">
-        <v>1000865.549504762</v>
+        <v>1081323.512137729</v>
       </c>
       <c r="M5" t="n">
-        <v>62432.42220986831</v>
+        <v>468.9527739732148</v>
       </c>
     </row>
     <row r="6">
@@ -1472,40 +1472,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.89119035502008</v>
+        <v>37.896</v>
       </c>
       <c r="C6" t="n">
-        <v>37.89119035502008</v>
+        <v>37.896</v>
       </c>
       <c r="D6" t="n">
-        <v>151999.7830011241</v>
+        <v>151989.4512511416</v>
       </c>
       <c r="E6" t="n">
-        <v>116917.3588680074</v>
+        <v>116950.5227328767</v>
       </c>
       <c r="F6" t="n">
-        <v>4011.480810630859</v>
+        <v>4010.699051381189</v>
       </c>
       <c r="G6" t="n">
-        <v>3085.607967777064</v>
+        <v>3086.091480179351</v>
       </c>
       <c r="H6" t="n">
-        <v>925.8728428537947</v>
+        <v>924.6075712018378</v>
       </c>
       <c r="I6" t="n">
-        <v>35082.42413311673</v>
+        <v>35038.92851826485</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>2279996.745016862</v>
+        <v>2279841.768767123</v>
       </c>
       <c r="L6" t="n">
-        <v>1753760.383020111</v>
+        <v>1754257.840993151</v>
       </c>
       <c r="M6" t="n">
-        <v>526236.3619967509</v>
+        <v>525583.9277739727</v>
       </c>
     </row>
     <row r="7">
@@ -1515,40 +1515,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.87684972099631</v>
+        <v>25.68289156626506</v>
       </c>
       <c r="C7" t="n">
-        <v>24.87684972099631</v>
+        <v>25.68289156626506</v>
       </c>
       <c r="D7" t="n">
-        <v>99237.15075778525</v>
+        <v>100469.8574198163</v>
       </c>
       <c r="E7" t="n">
-        <v>95105.84851608095</v>
+        <v>100267.9017015513</v>
       </c>
       <c r="F7" t="n">
-        <v>3989.136561532873</v>
+        <v>3911.937141524408</v>
       </c>
       <c r="G7" t="n">
-        <v>3823.066408437185</v>
+        <v>3904.073707699448</v>
       </c>
       <c r="H7" t="n">
-        <v>166.0701530956885</v>
+        <v>7.863433824960339</v>
       </c>
       <c r="I7" t="n">
-        <v>4131.302241704296</v>
+        <v>201.9557182649587</v>
       </c>
       <c r="J7" t="n">
         <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>1488557.261366779</v>
+        <v>1507047.861297244</v>
       </c>
       <c r="L7" t="n">
-        <v>1426587.727741214</v>
+        <v>1504018.525523269</v>
       </c>
       <c r="M7" t="n">
-        <v>61969.53362556444</v>
+        <v>3029.335773974381</v>
       </c>
     </row>
     <row r="8">
@@ -1558,40 +1558,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12.88950865549292</v>
+        <v>13.71555180722891</v>
       </c>
       <c r="C8" t="n">
-        <v>12.88950865549292</v>
+        <v>13.71555180722891</v>
       </c>
       <c r="D8" t="n">
-        <v>59357.82848827539</v>
+        <v>60621.12381499696</v>
       </c>
       <c r="E8" t="n">
-        <v>60563.43596438447</v>
+        <v>65853.58151673216</v>
       </c>
       <c r="F8" t="n">
-        <v>4605.12732290845</v>
+        <v>4419.88223784376</v>
       </c>
       <c r="G8" t="n">
-        <v>4698.661336371042</v>
+        <v>4801.380392294781</v>
       </c>
       <c r="H8" t="n">
-        <v>-93.53401346259216</v>
+        <v>-381.498154451021</v>
       </c>
       <c r="I8" t="n">
-        <v>-1205.607476109079</v>
+        <v>-5232.457701735191</v>
       </c>
       <c r="J8" t="n">
         <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>890367.4273241308</v>
+        <v>909316.8572249545</v>
       </c>
       <c r="L8" t="n">
-        <v>908451.539465767</v>
+        <v>987803.7227509824</v>
       </c>
       <c r="M8" t="n">
-        <v>-18084.11214163618</v>
+        <v>-78486.86552602786</v>
       </c>
     </row>
     <row r="9">
@@ -1601,40 +1601,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.71982399290108</v>
+        <v>10.1485156626506</v>
       </c>
       <c r="C9" t="n">
-        <v>8.71982399290108</v>
+        <v>10.1485156626506</v>
       </c>
       <c r="D9" t="n">
-        <v>44730.75074428493</v>
+        <v>46915.69653788854</v>
       </c>
       <c r="E9" t="n">
-        <v>55107.08054821382</v>
+        <v>64256.70773962372</v>
       </c>
       <c r="F9" t="n">
-        <v>5129.7767914468</v>
+        <v>4622.9121673972</v>
       </c>
       <c r="G9" t="n">
-        <v>6319.746888592842</v>
+        <v>6331.636061429803</v>
       </c>
       <c r="H9" t="n">
-        <v>-1189.970097146042</v>
+        <v>-1708.723894032602</v>
       </c>
       <c r="I9" t="n">
-        <v>-10376.32980392889</v>
+        <v>-17341.01120173519</v>
       </c>
       <c r="J9" t="n">
         <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>670961.261164274</v>
+        <v>703735.4480683281</v>
       </c>
       <c r="L9" t="n">
-        <v>826606.2082232073</v>
+        <v>963850.6160943558</v>
       </c>
       <c r="M9" t="n">
-        <v>-155644.9470589333</v>
+        <v>-260115.1680260278</v>
       </c>
     </row>
     <row r="10">
@@ -1650,34 +1650,34 @@
         <v>43.5693958360586</v>
       </c>
       <c r="D10" t="n">
-        <v>179728.6691933567</v>
+        <v>179745.3203044678</v>
       </c>
       <c r="E10" t="n">
         <v>125492.3720846543</v>
       </c>
       <c r="F10" t="n">
-        <v>4125.112725217339</v>
+        <v>4125.494899695355</v>
       </c>
       <c r="G10" t="n">
         <v>2880.287175816085</v>
       </c>
       <c r="H10" t="n">
-        <v>1244.825549401254</v>
+        <v>1245.20772387927</v>
       </c>
       <c r="I10" t="n">
-        <v>54236.29710870236</v>
+        <v>54252.94821981346</v>
       </c>
       <c r="J10" t="n">
         <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>2695930.037900351</v>
+        <v>2696179.804567017</v>
       </c>
       <c r="L10" t="n">
         <v>1882385.581269815</v>
       </c>
       <c r="M10" t="n">
-        <v>813544.4566305354</v>
+        <v>813794.223297202</v>
       </c>
     </row>
     <row r="11">
@@ -1816,40 +1816,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="C14" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="D14" t="n">
-        <v>200050.9070031401</v>
+        <v>200066.8181461275</v>
       </c>
       <c r="E14" t="n">
-        <v>129223.9203221591</v>
+        <v>129241.7037480154</v>
       </c>
       <c r="F14" t="n">
-        <v>4248.217072579292</v>
+        <v>4248.322283011702</v>
       </c>
       <c r="G14" t="n">
-        <v>2744.157838232672</v>
+        <v>2744.385175986858</v>
       </c>
       <c r="H14" t="n">
-        <v>1504.05923434662</v>
+        <v>1503.937107024844</v>
       </c>
       <c r="I14" t="n">
-        <v>70826.98668098106</v>
+        <v>70825.11439811208</v>
       </c>
       <c r="J14" t="n">
         <v>15</v>
       </c>
       <c r="K14" t="n">
-        <v>3000763.605047102</v>
+        <v>3001002.272191912</v>
       </c>
       <c r="L14" t="n">
-        <v>1938358.804832386</v>
+        <v>1938625.55622023</v>
       </c>
       <c r="M14" t="n">
-        <v>1062404.800214716</v>
+        <v>1062376.715971681</v>
       </c>
     </row>
     <row r="15">
@@ -1902,40 +1902,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.31929596953836</v>
+        <v>28.36974939759036</v>
       </c>
       <c r="C16" t="n">
-        <v>28.31929596953836</v>
+        <v>28.36974939759036</v>
       </c>
       <c r="D16" t="n">
-        <v>117685.2805538889</v>
+        <v>117762.4406631897</v>
       </c>
       <c r="E16" t="n">
-        <v>108959.1126809942</v>
+        <v>109282.2265249248</v>
       </c>
       <c r="F16" t="n">
-        <v>4155.657000812344</v>
+        <v>4150.9862851729</v>
       </c>
       <c r="G16" t="n">
-        <v>3847.521943984626</v>
+        <v>3852.06880023434</v>
       </c>
       <c r="H16" t="n">
-        <v>308.1350568277185</v>
+        <v>298.9174849385599</v>
       </c>
       <c r="I16" t="n">
-        <v>8726.167872894686</v>
+        <v>8480.214138264942</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>1765279.208308333</v>
+        <v>1766436.609947846</v>
       </c>
       <c r="L16" t="n">
-        <v>1634386.690214913</v>
+        <v>1639233.397873872</v>
       </c>
       <c r="M16" t="n">
-        <v>130892.5180934203</v>
+        <v>127203.2120739741</v>
       </c>
     </row>
     <row r="17">
@@ -1945,40 +1945,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23.64652488520101</v>
+        <v>23.69697831325301</v>
       </c>
       <c r="C17" t="n">
-        <v>23.64652488520101</v>
+        <v>23.69697831325301</v>
       </c>
       <c r="D17" t="n">
-        <v>102135.8559755756</v>
+        <v>102213.0160848765</v>
       </c>
       <c r="E17" t="n">
-        <v>94440.77356505507</v>
+        <v>94788.66424661153</v>
       </c>
       <c r="F17" t="n">
-        <v>4319.2755160187</v>
+        <v>4313.335427568494</v>
       </c>
       <c r="G17" t="n">
-        <v>3993.854235391691</v>
+        <v>4000.031691534236</v>
       </c>
       <c r="H17" t="n">
-        <v>325.4212806270089</v>
+        <v>313.3037360342582</v>
       </c>
       <c r="I17" t="n">
-        <v>7695.082410520554</v>
+        <v>7424.351838264964</v>
       </c>
       <c r="J17" t="n">
         <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>1532037.839633634</v>
+        <v>1533195.241273148</v>
       </c>
       <c r="L17" t="n">
-        <v>1416611.603475826</v>
+        <v>1421829.963699173</v>
       </c>
       <c r="M17" t="n">
-        <v>115426.2361578083</v>
+        <v>111365.2775739745</v>
       </c>
     </row>
     <row r="18">
@@ -1988,40 +1988,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.0251066794321</v>
+        <v>44.02381585306408</v>
       </c>
       <c r="C18" t="n">
-        <v>44.0251066794321</v>
+        <v>44.02381585306408</v>
       </c>
       <c r="D18" t="n">
-        <v>186337.009198309</v>
+        <v>186273.2822675455</v>
       </c>
       <c r="E18" t="n">
-        <v>120217.6934677869</v>
+        <v>120208.7928542453</v>
       </c>
       <c r="F18" t="n">
-        <v>4232.516926196637</v>
+        <v>4231.193472398208</v>
       </c>
       <c r="G18" t="n">
-        <v>2730.662172908508</v>
+        <v>2730.540061667069</v>
       </c>
       <c r="H18" t="n">
-        <v>1501.854753288129</v>
+        <v>1500.653410731139</v>
       </c>
       <c r="I18" t="n">
-        <v>66119.31573052207</v>
+        <v>66064.48941330018</v>
       </c>
       <c r="J18" t="n">
         <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>2795055.137974635</v>
+        <v>2794099.234013182</v>
       </c>
       <c r="L18" t="n">
-        <v>1803265.402016804</v>
+        <v>1803131.892813679</v>
       </c>
       <c r="M18" t="n">
-        <v>991789.735957831</v>
+        <v>990967.3411995027</v>
       </c>
     </row>
     <row r="19">
@@ -2289,40 +2289,40 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.88497590139153</v>
+        <v>12.50518554216867</v>
       </c>
       <c r="C25" t="n">
-        <v>11.88497590139153</v>
+        <v>12.50518554216867</v>
       </c>
       <c r="D25" t="n">
-        <v>58425.72906300299</v>
+        <v>59374.23634029818</v>
       </c>
       <c r="E25" t="n">
-        <v>56022.95370056832</v>
+        <v>59994.90028203334</v>
       </c>
       <c r="F25" t="n">
-        <v>4915.931639050471</v>
+        <v>4747.969243645575</v>
       </c>
       <c r="G25" t="n">
-        <v>4713.76249858521</v>
+        <v>4797.601769260027</v>
       </c>
       <c r="H25" t="n">
-        <v>202.1691404652611</v>
+        <v>-49.63252561445188</v>
       </c>
       <c r="I25" t="n">
-        <v>2402.775362434666</v>
+        <v>-620.6639417351616</v>
       </c>
       <c r="J25" t="n">
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>876385.9359450449</v>
+        <v>890613.5451044727</v>
       </c>
       <c r="L25" t="n">
-        <v>840344.3055085249</v>
+        <v>899923.5042305001</v>
       </c>
       <c r="M25" t="n">
-        <v>36041.63043651999</v>
+        <v>-9309.959126027425</v>
       </c>
     </row>
   </sheetData>
@@ -2386,25 +2386,25 @@
         <v>360</v>
       </c>
       <c r="B2" t="n">
-        <v>10029.35003668187</v>
+        <v>10117.60542876999</v>
       </c>
       <c r="C2" t="n">
-        <v>41959191.5481847</v>
+        <v>42093584.743102</v>
       </c>
       <c r="D2" t="n">
-        <v>35438298.52371</v>
+        <v>36011013.79057615</v>
       </c>
       <c r="E2" t="n">
-        <v>4183.640155615365</v>
+        <v>4160.429564035626</v>
       </c>
       <c r="F2" t="n">
-        <v>3533.459136842978</v>
+        <v>3559.242752062339</v>
       </c>
       <c r="G2" t="n">
-        <v>6520893.024474695</v>
+        <v>6082570.952525854</v>
       </c>
       <c r="H2" t="n">
-        <v>650.1810187723871</v>
+        <v>601.1868119732875</v>
       </c>
     </row>
   </sheetData>
@@ -14851,13 +14851,13 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>23.54527835858442</v>
+        <v>23.54656789412607</v>
       </c>
       <c r="E5" t="n">
-        <v>1976.48401826484</v>
+        <v>1988.094130375551</v>
       </c>
       <c r="F5" t="n">
-        <v>83.94396482232413</v>
+        <v>84.43243785314041</v>
       </c>
     </row>
     <row r="6">
@@ -14871,13 +14871,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="E6" t="n">
-        <v>1976.48401826484</v>
+        <v>1988.094130375551</v>
       </c>
       <c r="F6" t="n">
-        <v>41.97198241116207</v>
+        <v>42.21621892657021</v>
       </c>
     </row>
     <row r="7">
@@ -14891,13 +14891,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="E7" t="n">
-        <v>1976.48401826484</v>
+        <v>1988.094130375551</v>
       </c>
       <c r="F7" t="n">
-        <v>41.97198241116207</v>
+        <v>42.21621892657021</v>
       </c>
     </row>
     <row r="8">
@@ -14914,10 +14914,10 @@
         <v>23.8700777023745</v>
       </c>
       <c r="E8" t="n">
-        <v>3878.410482973325</v>
+        <v>3976.188260751102</v>
       </c>
       <c r="F8" t="n">
-        <v>162.4800108039663</v>
+        <v>166.5762596305067</v>
       </c>
     </row>
     <row r="9">
@@ -14934,10 +14934,10 @@
         <v>47.740155404749</v>
       </c>
       <c r="E9" t="n">
-        <v>3878.410482973325</v>
+        <v>3976.188260751102</v>
       </c>
       <c r="F9" t="n">
-        <v>81.24000540198317</v>
+        <v>83.28812981525333</v>
       </c>
     </row>
     <row r="10">
@@ -14954,10 +14954,10 @@
         <v>47.740155404749</v>
       </c>
       <c r="E10" t="n">
-        <v>3878.410482973325</v>
+        <v>3976.188260751102</v>
       </c>
       <c r="F10" t="n">
-        <v>81.24000540198317</v>
+        <v>83.28812981525333</v>
       </c>
     </row>
     <row r="11">
@@ -14971,13 +14971,13 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>24.1913880461879</v>
+        <v>24.19332041326082</v>
       </c>
       <c r="E11" t="n">
-        <v>5890.583006776788</v>
+        <v>5817.583006776788</v>
       </c>
       <c r="F11" t="n">
-        <v>243.4991739841498</v>
+        <v>240.4623634707065</v>
       </c>
     </row>
     <row r="12">
@@ -14991,13 +14991,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>48.38277609237579</v>
+        <v>48.38664082652165</v>
       </c>
       <c r="E12" t="n">
-        <v>5890.583006776788</v>
+        <v>5817.583006776788</v>
       </c>
       <c r="F12" t="n">
-        <v>121.7495869920749</v>
+        <v>120.2311817353533</v>
       </c>
     </row>
     <row r="13">
@@ -15011,13 +15011,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>48.38277609237579</v>
+        <v>48.38664082652165</v>
       </c>
       <c r="E13" t="n">
-        <v>5890.583006776788</v>
+        <v>5817.583006776788</v>
       </c>
       <c r="F13" t="n">
-        <v>121.7495869920749</v>
+        <v>120.2311817353533</v>
       </c>
     </row>
     <row r="14">
@@ -15214,10 +15214,10 @@
         <v>25.48584518640449</v>
       </c>
       <c r="E23" t="n">
-        <v>13794.13029119474</v>
+        <v>13860.62812785388</v>
       </c>
       <c r="F23" t="n">
-        <v>541.2467269695757</v>
+        <v>543.8559336163543</v>
       </c>
     </row>
     <row r="24">
@@ -15234,10 +15234,10 @@
         <v>50.97169037280898</v>
       </c>
       <c r="E24" t="n">
-        <v>13794.13029119474</v>
+        <v>13860.62812785388</v>
       </c>
       <c r="F24" t="n">
-        <v>270.6233634847878</v>
+        <v>271.9279668081771</v>
       </c>
     </row>
     <row r="25">
@@ -15254,10 +15254,10 @@
         <v>50.97169037280898</v>
       </c>
       <c r="E25" t="n">
-        <v>13794.13029119474</v>
+        <v>13860.62812785388</v>
       </c>
       <c r="F25" t="n">
-        <v>270.6233634847878</v>
+        <v>271.9279668081771</v>
       </c>
     </row>
     <row r="26">
@@ -15274,10 +15274,10 @@
         <v>25.8084481724546</v>
       </c>
       <c r="E26" t="n">
-        <v>15756.8751207707</v>
+        <v>15757.69633616033</v>
       </c>
       <c r="F26" t="n">
-        <v>610.5316761194512</v>
+        <v>610.5634957540198</v>
       </c>
     </row>
     <row r="27">
@@ -15294,10 +15294,10 @@
         <v>51.61689634490921</v>
       </c>
       <c r="E27" t="n">
-        <v>15756.8751207707</v>
+        <v>15757.69633616033</v>
       </c>
       <c r="F27" t="n">
-        <v>305.2658380597256</v>
+        <v>305.2817478770099</v>
       </c>
     </row>
     <row r="28">
@@ -15314,10 +15314,10 @@
         <v>51.61689634490921</v>
       </c>
       <c r="E28" t="n">
-        <v>15756.8751207707</v>
+        <v>15757.69633616033</v>
       </c>
       <c r="F28" t="n">
-        <v>305.2658380597256</v>
+        <v>305.2817478770099</v>
       </c>
     </row>
     <row r="29">
@@ -15334,10 +15334,10 @@
         <v>26.13105115850471</v>
       </c>
       <c r="E29" t="n">
-        <v>17719.619471306</v>
+        <v>17450.71947130601</v>
       </c>
       <c r="F29" t="n">
-        <v>678.1058811535374</v>
+        <v>667.8154416924949</v>
       </c>
     </row>
     <row r="30">
@@ -15354,10 +15354,10 @@
         <v>52.26210231700942</v>
       </c>
       <c r="E30" t="n">
-        <v>17719.619471306</v>
+        <v>17450.71947130601</v>
       </c>
       <c r="F30" t="n">
-        <v>339.0529405767687</v>
+        <v>333.9077208462475</v>
       </c>
     </row>
     <row r="31">
@@ -15374,10 +15374,10 @@
         <v>52.26210231700942</v>
       </c>
       <c r="E31" t="n">
-        <v>17719.619471306</v>
+        <v>17450.71947130601</v>
       </c>
       <c r="F31" t="n">
-        <v>339.0529405767687</v>
+        <v>333.9077208462475</v>
       </c>
     </row>
     <row r="32">
@@ -16019,7 +16019,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-4.197198241116206</v>
+        <v>-4.221621892657021</v>
       </c>
     </row>
     <row r="3">
@@ -16030,7 +16030,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>-3.92680229908211</v>
+        <v>-4.107191088868312</v>
       </c>
     </row>
     <row r="4">
@@ -16041,7 +16041,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.050958159009174</v>
+        <v>-3.694305192009993</v>
       </c>
     </row>
     <row r="5">
@@ -16052,7 +16052,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="n">
-        <v>-3.644183682453095</v>
+        <v>-3.79602420812526</v>
       </c>
     </row>
     <row r="6">
@@ -16085,7 +16085,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>-3.943640430166204</v>
+        <v>-4.074100762505134</v>
       </c>
     </row>
     <row r="9">
@@ -16096,7 +16096,7 @@
         <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>-3.464247457493775</v>
+        <v>-3.335378106883275</v>
       </c>
     </row>
     <row r="10">
@@ -16107,7 +16107,7 @@
         <v>90</v>
       </c>
       <c r="C10" t="n">
-        <v>-3.378710251704314</v>
+        <v>-2.862597296923758</v>
       </c>
     </row>
     <row r="11">
@@ -16118,7 +16118,7 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>-2.741832790629979</v>
+        <v>-3.256354763682106</v>
       </c>
     </row>
     <row r="12">
@@ -16744,13 +16744,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.88827855100043</v>
+        <v>13.89518216575682</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12.88827855100043</v>
+        <v>13.89518216575682</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16761,7 +16761,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>12.88827855100043</v>
+        <v>13.89518216575682</v>
       </c>
     </row>
     <row r="3">
@@ -16771,13 +16771,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.148200000000003</v>
+        <v>1.997887134132577</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8.148200000000003</v>
+        <v>1.997887134132577</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.148200000000003</v>
+        <v>1.997887134132577</v>
       </c>
     </row>
     <row r="4">
@@ -16798,13 +16798,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.148200000000003</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8.148200000000003</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.148200000000003</v>
+        <v>3.108624468950438e-15</v>
       </c>
     </row>
     <row r="5">
@@ -16825,13 +16825,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.916658603415248</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8.916658603415248</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.916658603415248</v>
+        <v>1.110223024625157e-15</v>
       </c>
     </row>
     <row r="6">
@@ -16852,13 +16852,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.4549290342064</v>
+        <v>9.955950608378847</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>11.4549290342064</v>
+        <v>9.955950608378847</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16869,7 +16869,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11.4549290342064</v>
+        <v>9.955950608378847</v>
       </c>
     </row>
     <row r="7">
@@ -16879,13 +16879,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.954929034206401</v>
+        <v>4.444777879086814e-14</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>8.954929034206401</v>
+        <v>4.444777879086814e-14</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16896,7 +16896,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.954929034206401</v>
+        <v>4.444777879086814e-14</v>
       </c>
     </row>
     <row r="8">
@@ -16906,13 +16906,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.166729034206401</v>
+        <v>2.203792703880936e-15</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>9.166729034206401</v>
+        <v>2.203792703880936e-15</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16923,7 +16923,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>9.166729034206401</v>
+        <v>2.203792703880936e-15</v>
       </c>
     </row>
     <row r="9">
@@ -16933,13 +16933,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15.85335047733332</v>
+        <v>2.737316546270246e-14</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>15.85335047733332</v>
+        <v>2.737316546270246e-14</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>15.85335047733332</v>
+        <v>2.737316546270246e-14</v>
       </c>
     </row>
     <row r="10">
@@ -16960,13 +16960,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.958175732143999</v>
+        <v>10.30983476234842</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>8.958175732143999</v>
+        <v>10.30983476234842</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16977,7 +16977,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.958175732143999</v>
+        <v>10.30983476234842</v>
       </c>
     </row>
     <row r="11">
@@ -17068,13 +17068,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.98499292804438</v>
+        <v>12.92512515899771</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98499292804438</v>
+        <v>12.92512515899771</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -17085,7 +17085,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>11.98499292804438</v>
+        <v>12.92512515899771</v>
       </c>
     </row>
     <row r="15">
@@ -17122,13 +17122,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17139,7 +17139,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -17149,13 +17149,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17166,7 +17166,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
     </row>
     <row r="18">
@@ -17176,13 +17176,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13.958175732144</v>
+        <v>8.940319300719713</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13.958175732144</v>
+        <v>8.940319300719713</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>13.958175732144</v>
+        <v>8.940319300719713</v>
       </c>
     </row>
     <row r="19">
@@ -17365,13 +17365,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.908400000000002</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.908400000000002</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17382,7 +17382,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6.908400000000002</v>
+        <v>3.108624468950438e-15</v>
       </c>
     </row>
   </sheetData>
@@ -17463,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5499478172386056</v>
+        <v>0.5497661908015011</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -17491,7 +17491,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.537692729549936</v>
+        <v>0.5374551776764638</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -17519,7 +17519,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.537692729549936</v>
+        <v>0.5374551776764638</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -17547,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.535694419209517</v>
+        <v>0.5356195879356871</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -17575,7 +17575,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5340421474074055</v>
+        <v>0.5339133746798372</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -17603,7 +17603,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5217847835983057</v>
+        <v>0.5216412802378768</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5200359770553477</v>
+        <v>0.5198436597315288</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -17659,7 +17659,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5111431775836763</v>
+        <v>0.5111304399302142</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -17668,26 +17668,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>discrete_Q45</t>
+          <t>offgrid_storage</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5363.375423971334</v>
+        <v>4160.429564035626</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>16200</v>
+        <v>10117.60542876999</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>392.0494630260221</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4535542084913343</v>
+        <v>0.4537670022521184</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -17696,26 +17696,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>offgrid_storage</t>
+          <t>discrete_Q45</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4183.640155615365</v>
+        <v>5363.375423971334</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>10029.35003668187</v>
+        <v>16200</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>466.9022458332986</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4535330409617602</v>
+        <v>0.4534762286746003</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -17743,7 +17743,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4524367003804987</v>
+        <v>0.4524118730042569</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
@@ -30081,34 +30081,34 @@
         <v>30.46155309645131</v>
       </c>
       <c r="J2" t="n">
-        <v>123.1560851741725</v>
+        <v>122.9388958565488</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>16.16101121107111</v>
+        <v>17.38510414345116</v>
       </c>
       <c r="M2" t="n">
-        <v>12.88827855100043</v>
+        <v>13.89518216575682</v>
       </c>
       <c r="N2" t="n">
-        <v>12.88827855100043</v>
+        <v>13.89518216575682</v>
       </c>
       <c r="O2" t="n">
         <v>0.05399871077760565</v>
       </c>
       <c r="P2" t="n">
-        <v>12.16791482582751</v>
+        <v>12.38510414345117</v>
       </c>
       <c r="Q2" t="n">
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>173529.4486494036</v>
+        <v>173541.6895787274</v>
       </c>
       <c r="S2" t="n">
-        <v>4177.562272665971</v>
+        <v>4177.856961809073</v>
       </c>
     </row>
     <row r="3">
@@ -30135,43 +30135,43 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>31.48301548127506</v>
+        <v>32.0372530120482</v>
       </c>
       <c r="H3" t="n">
-        <v>1.311792311719794</v>
+        <v>1.334885542168675</v>
       </c>
       <c r="I3" t="n">
-        <v>40.51698451872494</v>
+        <v>39.9627469879518</v>
       </c>
       <c r="J3" t="n">
         <v>4.950200000000002</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6.150312865867431</v>
       </c>
       <c r="L3" t="n">
-        <v>10.16695250902834</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>8.148200000000003</v>
+        <v>1.997887134132577</v>
       </c>
       <c r="N3" t="n">
-        <v>8.148200000000003</v>
+        <v>1.997887134132577</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5542375307731398</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>2.500000000000006</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.113456336641722</v>
+        <v>2.249999999999983</v>
       </c>
       <c r="R3" t="n">
-        <v>125673.2002605049</v>
+        <v>126520.8141909006</v>
       </c>
       <c r="S3" t="n">
-        <v>3991.7777360066</v>
+        <v>3949.177981748938</v>
       </c>
     </row>
     <row r="4">
@@ -30198,43 +30198,43 @@
         <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>19.8579184230318</v>
+        <v>20.59317108433735</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8274132676263249</v>
+        <v>0.8580487951807229</v>
       </c>
       <c r="I4" t="n">
-        <v>52.1420815769682</v>
+        <v>51.40682891566265</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8.148200000000015</v>
       </c>
       <c r="L4" t="n">
-        <v>10.17099514806009</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>8.148200000000003</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="N4" t="n">
-        <v>8.148200000000003</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7352526613055517</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>7.993605777301127e-15</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.113456336641722</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>86395.25382609818</v>
+        <v>87519.70022945481</v>
       </c>
       <c r="S4" t="n">
-        <v>4350.670195416576</v>
+        <v>4249.937995028852</v>
       </c>
     </row>
     <row r="5">
@@ -30261,43 +30261,43 @@
         <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>15.2036679576071</v>
+        <v>16.00987951807229</v>
       </c>
       <c r="H5" t="n">
-        <v>0.633486164900296</v>
+        <v>0.6670783132530121</v>
       </c>
       <c r="I5" t="n">
-        <v>56.7963320423929</v>
+        <v>55.9901204819277</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4693413965847555</v>
+        <v>9.386000000000047</v>
       </c>
       <c r="L5" t="n">
-        <v>11.15259325310172</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.916658603415248</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="N5" t="n">
-        <v>8.916658603415248</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8062115604651847</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P5" t="n">
         <v>2.664535259100376e-15</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>70886.53144764202</v>
+        <v>72119.49766078012</v>
       </c>
       <c r="S5" t="n">
-        <v>4662.462482428405</v>
+        <v>4504.687095200817</v>
       </c>
     </row>
     <row r="6">
@@ -30324,43 +30324,43 @@
         <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>37.89119035502008</v>
+        <v>37.896</v>
       </c>
       <c r="H6" t="n">
-        <v>1.578799598125837</v>
+        <v>1.579</v>
       </c>
       <c r="I6" t="n">
-        <v>34.10880964497992</v>
+        <v>34.104</v>
       </c>
       <c r="J6" t="n">
-        <v>77.84326996281473</v>
+        <v>78.16648380128248</v>
       </c>
       <c r="K6" t="n">
-        <v>6.701070965793601</v>
+        <v>6.754533192903661</v>
       </c>
       <c r="L6" t="n">
-        <v>14.33526345940747</v>
+        <v>12.5</v>
       </c>
       <c r="M6" t="n">
-        <v>11.4549290342064</v>
+        <v>9.955950608378847</v>
       </c>
       <c r="N6" t="n">
-        <v>11.4549290342064</v>
+        <v>9.955950608378847</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.004809644979921757</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>11.76873003718525</v>
+        <v>11.4455161987175</v>
       </c>
       <c r="Q6" t="n">
         <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>151999.7830011241</v>
+        <v>151989.4512511416</v>
       </c>
       <c r="S6" t="n">
-        <v>4011.480810630859</v>
+        <v>4010.699051381189</v>
       </c>
     </row>
     <row r="7">
@@ -30387,43 +30387,43 @@
         <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>24.87684972099631</v>
+        <v>25.68289156626506</v>
       </c>
       <c r="H7" t="n">
-        <v>1.036535405041513</v>
+        <v>1.070120481927711</v>
       </c>
       <c r="I7" t="n">
-        <v>47.12315027900369</v>
+        <v>46.31710843373494</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>6.701070965793601</v>
+        <v>15.65599999999996</v>
       </c>
       <c r="L7" t="n">
-        <v>11.15024552621767</v>
+        <v>5.219117720870115e-14</v>
       </c>
       <c r="M7" t="n">
-        <v>8.954929034206401</v>
+        <v>4.444777879086814e-14</v>
       </c>
       <c r="N7" t="n">
-        <v>8.954929034206401</v>
+        <v>4.444777879086814e-14</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8060418452687479</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P7" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>99237.15075778525</v>
+        <v>100469.8574198163</v>
       </c>
       <c r="S7" t="n">
-        <v>3989.136561532873</v>
+        <v>3911.937141524408</v>
       </c>
     </row>
     <row r="8">
@@ -30450,43 +30450,43 @@
         <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>12.88950865549292</v>
+        <v>13.71555180722891</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5370628606455382</v>
+        <v>0.5714813253012048</v>
       </c>
       <c r="I8" t="n">
-        <v>59.11049134450708</v>
+        <v>58.28444819277109</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.701070965793601</v>
+        <v>15.8678</v>
       </c>
       <c r="L8" t="n">
-        <v>11.4269302656813</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9.166729034206401</v>
+        <v>2.203792703880936e-15</v>
       </c>
       <c r="N8" t="n">
-        <v>9.166729034206401</v>
+        <v>2.203792703880936e-15</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8260431517359983</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>59357.82848827539</v>
+        <v>60621.12381499696</v>
       </c>
       <c r="S8" t="n">
-        <v>4605.12732290845</v>
+        <v>4419.88223784376</v>
       </c>
     </row>
     <row r="9">
@@ -30513,43 +30513,43 @@
         <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>8.71982399290108</v>
+        <v>10.1485156626506</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3633259997042117</v>
+        <v>0.4228548192771084</v>
       </c>
       <c r="I9" t="n">
-        <v>63.28017600709892</v>
+        <v>61.8514843373494</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>15.31044952266669</v>
+        <v>31.16380000000003</v>
       </c>
       <c r="L9" t="n">
-        <v>19.76356809820172</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>15.85335047733332</v>
+        <v>2.737316546270246e-14</v>
       </c>
       <c r="N9" t="n">
-        <v>15.85335047733332</v>
+        <v>2.737316546270246e-14</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.428691669749522</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>44730.75074428493</v>
+        <v>46915.69653788854</v>
       </c>
       <c r="S9" t="n">
-        <v>5129.7767914468</v>
+        <v>4622.9121673972</v>
       </c>
     </row>
     <row r="10">
@@ -30585,34 +30585,34 @@
         <v>28.4306041639414</v>
       </c>
       <c r="J10" t="n">
-        <v>115.1197180385267</v>
+        <v>114.80626595762</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>11.24848196147324</v>
+        <v>12.91359307258436</v>
       </c>
       <c r="M10" t="n">
-        <v>8.958175732143999</v>
+        <v>10.30983476234842</v>
       </c>
       <c r="N10" t="n">
-        <v>8.958175732143999</v>
+        <v>10.30983476234842</v>
       </c>
       <c r="O10" t="n">
         <v>0.647578968588725</v>
       </c>
       <c r="P10" t="n">
-        <v>11.24848196147323</v>
+        <v>11.56193404237993</v>
       </c>
       <c r="Q10" t="n">
         <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>179728.6691933567</v>
+        <v>179745.3203044678</v>
       </c>
       <c r="S10" t="n">
-        <v>4125.112725217339</v>
+        <v>4125.494899695355</v>
       </c>
     </row>
     <row r="11">
@@ -30828,43 +30828,43 @@
         <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>47.09055671716884</v>
+        <v>47.09313578825215</v>
       </c>
       <c r="H14" t="n">
-        <v>1.962106529882035</v>
+        <v>1.962213991177173</v>
       </c>
       <c r="I14" t="n">
-        <v>24.90944328283116</v>
+        <v>24.90686421174785</v>
       </c>
       <c r="J14" t="n">
-        <v>161.7696250072087</v>
+        <v>161.5130688771052</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>15</v>
+        <v>16.16101121107111</v>
       </c>
       <c r="M14" t="n">
-        <v>11.98499292804438</v>
+        <v>12.92512515899771</v>
       </c>
       <c r="N14" t="n">
-        <v>11.98499292804438</v>
+        <v>12.92512515899771</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6041326207832896</v>
+        <v>0.6067116918666002</v>
       </c>
       <c r="P14" t="n">
-        <v>11.93637499279126</v>
+        <v>12.19293112289475</v>
       </c>
       <c r="Q14" t="n">
         <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>200050.9070031401</v>
+        <v>200066.8181461275</v>
       </c>
       <c r="S14" t="n">
-        <v>4248.217072579292</v>
+        <v>4248.322283011702</v>
       </c>
     </row>
     <row r="15">
@@ -30954,43 +30954,43 @@
         <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>28.31929596953836</v>
+        <v>28.36974939759036</v>
       </c>
       <c r="H16" t="n">
-        <v>1.179970665397432</v>
+        <v>1.182072891566265</v>
       </c>
       <c r="I16" t="n">
-        <v>43.68070403046164</v>
+        <v>43.63025060240964</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.5642000000000078</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6979390880526496</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.05045342805200193</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>4.440892098500626e-15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6281451792473847</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>117685.2805538889</v>
+        <v>117762.4406631897</v>
       </c>
       <c r="S16" t="n">
-        <v>4155.657000812344</v>
+        <v>4150.9862851729</v>
       </c>
     </row>
     <row r="17">
@@ -31017,43 +31017,43 @@
         <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>23.64652488520101</v>
+        <v>23.69697831325301</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9852718702167088</v>
+        <v>0.9873740963855419</v>
       </c>
       <c r="I17" t="n">
-        <v>48.35347511479899</v>
+        <v>48.30302168674699</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.5641999999999482</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6979390880526496</v>
+        <v>6.525644222518975e-14</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.05045342805199837</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P17" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6281451792473847</v>
+        <v>5.871252913571023e-14</v>
       </c>
       <c r="R17" t="n">
-        <v>102135.8559755756</v>
+        <v>102213.0160848765</v>
       </c>
       <c r="S17" t="n">
-        <v>4319.2755160187</v>
+        <v>4313.335427568494</v>
       </c>
     </row>
     <row r="18">
@@ -31080,43 +31080,43 @@
         <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>44.0251066794321</v>
+        <v>44.02381585306408</v>
       </c>
       <c r="H18" t="n">
-        <v>1.834379444976338</v>
+        <v>1.834325660544337</v>
       </c>
       <c r="I18" t="n">
-        <v>27.9748933205679</v>
+        <v>27.97618414693592</v>
       </c>
       <c r="J18" t="n">
-        <v>146.2590958565488</v>
+        <v>147.4165221222622</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>17.38510414345116</v>
+        <v>11.22767787773778</v>
       </c>
       <c r="M18" t="n">
-        <v>13.958175732144</v>
+        <v>8.940319300719713</v>
       </c>
       <c r="N18" t="n">
-        <v>13.958175732144</v>
+        <v>8.940319300719713</v>
       </c>
       <c r="O18" t="n">
-        <v>0.647578968588725</v>
+        <v>0.6462881422207047</v>
       </c>
       <c r="P18" t="n">
-        <v>12.38510414345117</v>
+        <v>11.22767787773779</v>
       </c>
       <c r="Q18" t="n">
         <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>186337.009198309</v>
+        <v>186273.2822675455</v>
       </c>
       <c r="S18" t="n">
-        <v>4232.516926196637</v>
+        <v>4231.193472398208</v>
       </c>
     </row>
     <row r="19">
@@ -31521,43 +31521,43 @@
         <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>11.88497590139153</v>
+        <v>12.50518554216867</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4952073292246469</v>
+        <v>0.5210493975903614</v>
       </c>
       <c r="I25" t="n">
-        <v>60.11502409860847</v>
+        <v>59.49481445783132</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>6.908400000000009</v>
       </c>
       <c r="L25" t="n">
-        <v>8.579566697417217</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>6.908400000000002</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="N25" t="n">
-        <v>6.908400000000002</v>
+        <v>3.108624468950438e-15</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6202096407771478</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>8.881784197001252e-16</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.459674950084906</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>58425.72906300299</v>
+        <v>59374.23634029818</v>
       </c>
       <c r="S25" t="n">
-        <v>4915.931639050471</v>
+        <v>4747.969243645575</v>
       </c>
     </row>
   </sheetData>
@@ -32310,16 +32310,16 @@
         <v>41.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1.161011211071108</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>6.177312132258225</v>
       </c>
       <c r="N13" t="n">
-        <v>16.21498878892889</v>
+        <v>19.876</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -32369,19 +32369,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49309638524361</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>8.321004016395991</v>
+        <v>3.387179730215932</v>
       </c>
       <c r="N14" t="n">
-        <v>21.60929638524362</v>
+        <v>22.61620000000001</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -32422,16 +32422,16 @@
         <v>41.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2.499999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.526584230585421</v>
+        <v>5.630405370755499</v>
       </c>
       <c r="N15" t="n">
-        <v>29.1502</v>
+        <v>24.1502</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -32484,7 +32484,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>7.765531062124251</v>
+        <v>7.869144560013988</v>
       </c>
       <c r="N16" t="n">
         <v>11.55799999999999</v>
@@ -32534,7 +32534,7 @@
         <v>41.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.499999999999999</v>
+        <v>2.385104143451158</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -32543,7 +32543,7 @@
         <v>10</v>
       </c>
       <c r="N17" t="n">
-        <v>8.155799999999999</v>
+        <v>8.270695856548841</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -33704,10 +33704,10 @@
         <v>44.396</v>
       </c>
       <c r="I38" t="n">
-        <v>2.973701204819277</v>
+        <v>2.973701204819278</v>
       </c>
       <c r="J38" t="n">
-        <v>41.1362</v>
+        <v>41.13620000000002</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -33725,7 +33725,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
     </row>
     <row r="39">
@@ -33772,7 +33772,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.25</v>
+        <v>2.249999999999983</v>
       </c>
       <c r="N39" t="n">
         <v>4.950200000000002</v>
@@ -33828,7 +33828,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.2455</v>
+        <v>2.245499999999983</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -33872,19 +33872,19 @@
         <v>36.776</v>
       </c>
       <c r="I41" t="n">
-        <v>2.370278131877469</v>
+        <v>2.382346987951807</v>
       </c>
       <c r="J41" t="n">
-        <v>32.78884749097165</v>
+        <v>32.9558</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1669525090283417</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>2.391266258125508</v>
+        <v>2.241008999999983</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -33893,7 +33893,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-1.942890293094024e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -33928,19 +33928,19 @@
         <v>29.308</v>
       </c>
       <c r="I42" t="n">
-        <v>1.666843373493976</v>
+        <v>1.847566265060241</v>
       </c>
       <c r="J42" t="n">
-        <v>23.058</v>
+        <v>25.558</v>
       </c>
       <c r="K42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4.636483725609256</v>
+        <v>2.236526981999983</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -33984,19 +33984,19 @@
         <v>15.984</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7477734939759034</v>
+        <v>0.9284963855421684</v>
       </c>
       <c r="J43" t="n">
-        <v>10.3442</v>
+        <v>12.8442</v>
       </c>
       <c r="K43" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>6.877210758158038</v>
+        <v>2.232053928035983</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -34040,19 +34040,19 @@
         <v>9.628</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3266024096385542</v>
+        <v>0.5073253012048253</v>
       </c>
       <c r="J44" t="n">
-        <v>4.518000000000001</v>
+        <v>7.018000000000084</v>
       </c>
       <c r="K44" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>9.113456336641722</v>
+        <v>2.227589820179836</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -34061,7 +34061,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>-8.348877145181177e-14</v>
       </c>
     </row>
     <row r="45">
@@ -34108,7 +34108,7 @@
         <v>0.5338000000000007</v>
       </c>
       <c r="M45" t="n">
-        <v>8.502118312857327</v>
+        <v>1.630023529428365</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -34161,16 +34161,16 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2.258</v>
+        <v>1.46408713413257</v>
       </c>
       <c r="M46" t="n">
-        <v>5.976225187342723</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.7939128658674305</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -34217,16 +34217,16 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2.088200000000001</v>
+        <v>2.220446049250313e-15</v>
       </c>
       <c r="M47" t="n">
-        <v>3.644050514745815</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.088199999999998</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -34273,19 +34273,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8300000000000005</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.7145401914941</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>0.8300000000000054</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.329070518200751e-15</v>
       </c>
     </row>
     <row r="49">
@@ -34329,7 +34329,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2.438200000000001</v>
+        <v>3.996802888650564e-15</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -34338,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.438199999999997</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -35160,19 +35160,19 @@
         <v>18.228</v>
       </c>
       <c r="I64" t="n">
-        <v>0.915846133875174</v>
+        <v>1.055277108433735</v>
       </c>
       <c r="J64" t="n">
-        <v>12.66920485193991</v>
+        <v>14.598</v>
       </c>
       <c r="K64" t="n">
-        <v>1.928795148060091</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1.735915633254082</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -35181,7 +35181,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>-1.77635683940025e-15</v>
       </c>
     </row>
     <row r="65">
@@ -35216,19 +35216,19 @@
         <v>18.216</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8599373493975901</v>
+        <v>1.040660240963855</v>
       </c>
       <c r="J65" t="n">
-        <v>11.8958</v>
+        <v>14.3958</v>
       </c>
       <c r="K65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.982443801987574</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -35272,19 +35272,19 @@
         <v>15.228</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6490120481927709</v>
+        <v>0.829734939759036</v>
       </c>
       <c r="J66" t="n">
-        <v>8.977999999999998</v>
+        <v>11.478</v>
       </c>
       <c r="K66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>6.224478914383599</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -35328,19 +35328,19 @@
         <v>9.584</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>0.4658457831325302</v>
       </c>
       <c r="J67" t="n">
-        <v>4.15</v>
+        <v>6.444200000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>2.294199999999999</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>8.27680995655483</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -35349,7 +35349,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
     </row>
     <row r="68">
@@ -35384,19 +35384,19 @@
         <v>7.708000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3</v>
+        <v>0.3685301204819288</v>
       </c>
       <c r="J68" t="n">
-        <v>4.15</v>
+        <v>5.098000000000016</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9480000000000004</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>9.113456336641722</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>-1.509903313490213e-14</v>
       </c>
     </row>
     <row r="69">
@@ -35449,19 +35449,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5338000000000007</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>8.502118312857327</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>0.5338000000000139</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.243449787580175e-14</v>
       </c>
     </row>
     <row r="70">
@@ -35505,16 +35505,16 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
+        <v>8.881784197001252e-16</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
         <v>2.258</v>
-      </c>
-      <c r="M70" t="n">
-        <v>5.976225187342723</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -35561,19 +35561,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>2.088200000000001</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.644050514745814</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>2.088200000000002</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.77635683940025e-15</v>
       </c>
     </row>
     <row r="72">
@@ -35617,16 +35617,16 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0.8300000000000005</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>2.7145401914941</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>0.8300000000000014</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -35673,7 +35673,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>2.438200000000001</v>
+        <v>2.220446049250313e-15</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -35682,7 +35682,7 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2.438199999999998</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -36392,19 +36392,19 @@
         <v>13.676</v>
       </c>
       <c r="I86" t="n">
-        <v>0.6485498853179478</v>
+        <v>0.7529783132530121</v>
       </c>
       <c r="J86" t="n">
-        <v>8.971606746898278</v>
+        <v>10.4162</v>
       </c>
       <c r="K86" t="n">
-        <v>1.444593253101723</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>1.300133927791551</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
         <v>0</v>
@@ -36413,7 +36413,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>6.661338147750939e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -36448,19 +36448,19 @@
         <v>22.2</v>
       </c>
       <c r="I87" t="n">
-        <v>1.229653012048193</v>
+        <v>1.410375903614458</v>
       </c>
       <c r="J87" t="n">
-        <v>17.0102</v>
+        <v>19.5102</v>
       </c>
       <c r="K87" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.547533659935968</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -36504,19 +36504,19 @@
         <v>11.828</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4119036144578314</v>
+        <v>0.5926265060240964</v>
       </c>
       <c r="J88" t="n">
-        <v>5.698</v>
+        <v>8.198</v>
       </c>
       <c r="K88" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>5.790438592616096</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
@@ -36560,19 +36560,19 @@
         <v>12.456</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4435518072289155</v>
+        <v>0.6242746987951805</v>
       </c>
       <c r="J89" t="n">
-        <v>6.135799999999998</v>
+        <v>8.635799999999998</v>
       </c>
       <c r="K89" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>8.028857715430863</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -36616,19 +36616,19 @@
         <v>10.108</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3</v>
+        <v>0.4596144578313288</v>
       </c>
       <c r="J90" t="n">
-        <v>4.15</v>
+        <v>6.358000000000049</v>
       </c>
       <c r="K90" t="n">
-        <v>2.207999999999998</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -36637,7 +36637,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>-4.973799150320701e-14</v>
       </c>
     </row>
     <row r="91">
@@ -36681,19 +36681,19 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.905800000000001</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>8.973555555555555</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>0.9058000000000411</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.996802888650564e-14</v>
       </c>
     </row>
     <row r="92">
@@ -36737,16 +36737,16 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.3319999999999994</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="M92" t="n">
-        <v>8.586719555555556</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>0.3319999999999987</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -36793,16 +36793,16 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.5338000000000007</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>7.976435005333332</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>0.5338000000000008</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -36849,19 +36849,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2.258</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>5.451593246433776</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>2.258000000000001</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.77635683940025e-15</v>
       </c>
     </row>
     <row r="95">
@@ -36905,16 +36905,16 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2.088200000000001</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="M95" t="n">
-        <v>3.120467837718686</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2.0882</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -36961,16 +36961,16 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.8300000000000005</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>2.192004679821026</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>0.8300000000000006</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -37017,7 +37017,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1.968858603415245</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -37026,10 +37026,10 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>0.4693413965847555</v>
+        <v>2.438200000000004</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
     </row>
     <row r="98">
@@ -37580,7 +37580,7 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>2.25</v>
+        <v>2.249999999999997</v>
       </c>
       <c r="N107" t="n">
         <v>2.739999999999995</v>
@@ -37636,7 +37636,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.4955</v>
+        <v>4.495499999999996</v>
       </c>
       <c r="N108" t="n">
         <v>9.695799999999998</v>
@@ -37686,13 +37686,13 @@
         <v>41.5</v>
       </c>
       <c r="K109" t="n">
-        <v>2.499999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>6.736508999999999</v>
+        <v>6.736508999999995</v>
       </c>
       <c r="N109" t="n">
         <v>11.432</v>
@@ -37742,16 +37742,16 @@
         <v>41.5</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L110" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.945258204222221</v>
+        <v>8.973035981999997</v>
       </c>
       <c r="N110" t="n">
-        <v>18.2282</v>
+        <v>13.2282</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -37798,16 +37798,16 @@
         <v>41.5</v>
       </c>
       <c r="K111" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>6.187367687813777</v>
+        <v>8.955089910036</v>
       </c>
       <c r="N111" t="n">
-        <v>16.4182</v>
+        <v>18.9182</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -37854,16 +37854,16 @@
         <v>41.5</v>
       </c>
       <c r="K112" t="n">
-        <v>2.500000000000002</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.054483801282508</v>
       </c>
       <c r="M112" t="n">
-        <v>8.424992952438153</v>
+        <v>7.765531062124253</v>
       </c>
       <c r="N112" t="n">
-        <v>13.21399999999999</v>
+        <v>16.7684838012825</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -37910,7 +37910,7 @@
         <v>41.5</v>
       </c>
       <c r="K113" t="n">
-        <v>1.768730037185249</v>
+        <v>2.499999999999998</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -37919,7 +37919,7 @@
         <v>10</v>
       </c>
       <c r="N113" t="n">
-        <v>6.115069962814744</v>
+        <v>5.383799999999995</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -38072,19 +38072,19 @@
         <v>17.772</v>
       </c>
       <c r="I116" t="n">
-        <v>1.091238547791165</v>
+        <v>1.096048192771086</v>
       </c>
       <c r="J116" t="n">
-        <v>15.09546657777778</v>
+        <v>15.16200000000002</v>
       </c>
       <c r="K116" t="n">
-        <v>0.06653342222222136</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>10</v>
+        <v>9.940119919999979</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -38093,7 +38093,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>-2.309263891220326e-14</v>
       </c>
     </row>
     <row r="117">
@@ -38140,7 +38140,7 @@
         <v>1.9578</v>
       </c>
       <c r="M117" t="n">
-        <v>7.804666666666667</v>
+        <v>7.744906346826647</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -38184,10 +38184,10 @@
         <v>2.328</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>4.15</v>
+        <v>4.149999999999999</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -38196,13 +38196,13 @@
         <v>2.5</v>
       </c>
       <c r="M118" t="n">
-        <v>5.011279555555555</v>
+        <v>4.951638756355216</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>1.182</v>
+        <v>1.181999999999998</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>2.5</v>
       </c>
       <c r="M119" t="n">
-        <v>2.223479218666666</v>
+        <v>2.163957701064728</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -38305,7 +38305,7 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>1.9971290342064</v>
+        <v>1.943666807096338</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -38314,7 +38314,7 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>1.588870965793601</v>
+        <v>1.642333192903662</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
@@ -38417,7 +38417,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>4.382605389707805e-14</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -38426,7 +38426,7 @@
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0.2078000000000002</v>
+        <v>0.2077999999999564</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -39192,19 +39192,19 @@
         <v>40.364</v>
       </c>
       <c r="I136" t="n">
-        <v>2.572319600514385</v>
+        <v>2.655469879518072</v>
       </c>
       <c r="J136" t="n">
-        <v>35.58375447378233</v>
+        <v>36.734</v>
       </c>
       <c r="K136" t="n">
-        <v>1.150245526217675</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>1.035220973595907</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
@@ -39213,7 +39213,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -39248,19 +39248,19 @@
         <v>34.004</v>
       </c>
       <c r="I137" t="n">
-        <v>2.001238554216868</v>
+        <v>2.181961445783133</v>
       </c>
       <c r="J137" t="n">
-        <v>27.68380000000001</v>
+        <v>30.18380000000001</v>
       </c>
       <c r="K137" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.283150531648715</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -39304,19 +39304,19 @@
         <v>25.096</v>
       </c>
       <c r="I138" t="n">
-        <v>1.362361445783133</v>
+        <v>1.543084337349397</v>
       </c>
       <c r="J138" t="n">
-        <v>18.846</v>
+        <v>21.346</v>
       </c>
       <c r="K138" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>5.526584230585418</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -39360,19 +39360,19 @@
         <v>16.208</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7639662650602408</v>
+        <v>0.9446891566265058</v>
       </c>
       <c r="J139" t="n">
-        <v>10.5682</v>
+        <v>13.0682</v>
       </c>
       <c r="K139" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>7.765531062124248</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -39416,19 +39416,19 @@
         <v>9.452</v>
       </c>
       <c r="I140" t="n">
-        <v>0.3138795180722892</v>
+        <v>0.4946024096385505</v>
       </c>
       <c r="J140" t="n">
-        <v>4.342000000000001</v>
+        <v>6.841999999999948</v>
       </c>
       <c r="K140" t="n">
-        <v>2.5</v>
+        <v>5.219117720870115e-14</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -39437,7 +39437,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.113495536062349e-16</v>
       </c>
     </row>
     <row r="141">
@@ -39481,16 +39481,16 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
         <v>1.9578</v>
-      </c>
-      <c r="M141" t="n">
-        <v>7.804666666666667</v>
-      </c>
-      <c r="N141" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" t="n">
-        <v>0</v>
       </c>
       <c r="P141" t="n">
         <v>0</v>
@@ -39528,25 +39528,25 @@
         <v>2.328</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>4.15</v>
+        <v>4.149999999999999</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>5.011279555555556</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>1.182</v>
+        <v>3.681999999999998</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -39593,16 +39593,16 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>2.223479218666667</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>1.7882</v>
+        <v>4.2882</v>
       </c>
       <c r="P143" t="n">
         <v>0</v>
@@ -39649,7 +39649,7 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>1.997129034206401</v>
+        <v>3.996802888650563e-16</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -39658,7 +39658,7 @@
         <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1.5888709657936</v>
+        <v>3.586</v>
       </c>
       <c r="P144" t="n">
         <v>0</v>
@@ -40144,19 +40144,19 @@
         <v>8.92</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3822502053638737</v>
+        <v>0.4011903614457831</v>
       </c>
       <c r="J153" t="n">
-        <v>5.287794507533586</v>
+        <v>5.5498</v>
       </c>
       <c r="K153" t="n">
-        <v>0.2620054924664146</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0.2358049432197731</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -40209,7 +40209,7 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0.2118000000000002</v>
+        <v>1.582067810090848e-15</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -40218,7 +40218,7 @@
         <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>0.2117999999999986</v>
       </c>
       <c r="P154" t="n">
         <v>0</v>
@@ -40480,19 +40480,19 @@
         <v>20.868</v>
       </c>
       <c r="I159" t="n">
-        <v>1.285682546514586</v>
+        <v>1.314086746987952</v>
       </c>
       <c r="J159" t="n">
-        <v>17.78527522678511</v>
+        <v>18.1782</v>
       </c>
       <c r="K159" t="n">
-        <v>0.3929247732148899</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>0.3536322958934009</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -40501,7 +40501,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -40536,19 +40536,19 @@
         <v>19.884</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9942650602409639</v>
+        <v>1.174987951807229</v>
       </c>
       <c r="J160" t="n">
-        <v>13.754</v>
+        <v>16.254</v>
       </c>
       <c r="K160" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>2.602925031301614</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -40592,19 +40592,19 @@
         <v>15.444</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6595518072289156</v>
+        <v>0.8402746987951807</v>
       </c>
       <c r="J161" t="n">
-        <v>9.123799999999999</v>
+        <v>11.6238</v>
       </c>
       <c r="K161" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.847719181239011</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
         <v>0</v>
@@ -40648,19 +40648,19 @@
         <v>11.016</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3445301204819277</v>
+        <v>0.5252530120481927</v>
       </c>
       <c r="J162" t="n">
-        <v>4.766</v>
+        <v>7.266</v>
       </c>
       <c r="K162" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>7.088023742876533</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
         <v>0</v>
@@ -40704,19 +40704,19 @@
         <v>9.808</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3013156626506024</v>
+        <v>0.4820385542168674</v>
       </c>
       <c r="J163" t="n">
-        <v>4.1682</v>
+        <v>6.6682</v>
       </c>
       <c r="K163" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>9.32384769539078</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
         <v>0</v>
@@ -40760,19 +40760,19 @@
         <v>7.532</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3</v>
+        <v>0.3558072289156627</v>
       </c>
       <c r="J164" t="n">
-        <v>4.15</v>
+        <v>4.922000000000001</v>
       </c>
       <c r="K164" t="n">
-        <v>0.7720000000000002</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
         <v>0</v>
@@ -40825,16 +40825,16 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
         <v>1.9578</v>
-      </c>
-      <c r="M165" t="n">
-        <v>7.804666666666667</v>
-      </c>
-      <c r="N165" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="n">
-        <v>0</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -40872,25 +40872,25 @@
         <v>2.328</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>4.15</v>
+        <v>4.149999999999999</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>5.011279555555556</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
         <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>1.182</v>
+        <v>3.681999999999998</v>
       </c>
       <c r="P166" t="n">
         <v>0</v>
@@ -40937,16 +40937,16 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>2.223479218666667</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
       </c>
       <c r="O167" t="n">
-        <v>1.7882</v>
+        <v>4.2882</v>
       </c>
       <c r="P167" t="n">
         <v>0</v>
@@ -40993,7 +40993,7 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>1.997129034206401</v>
+        <v>3.996802888650563e-16</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -41002,7 +41002,7 @@
         <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>1.5888709657936</v>
+        <v>3.586</v>
       </c>
       <c r="P168" t="n">
         <v>0</v>
@@ -41208,19 +41208,19 @@
         <v>9.379999999999999</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5434866435034899</v>
+        <v>0.620255421686747</v>
       </c>
       <c r="J172" t="n">
-        <v>7.518231901798277</v>
+        <v>8.5802</v>
       </c>
       <c r="K172" t="n">
-        <v>1.061968098201723</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>0.9557712883815503</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
         <v>0</v>
@@ -41264,19 +41264,19 @@
         <v>10.304</v>
       </c>
       <c r="I173" t="n">
-        <v>0.492578313253012</v>
+        <v>0.6733012048192771</v>
       </c>
       <c r="J173" t="n">
-        <v>6.814</v>
+        <v>9.314</v>
       </c>
       <c r="K173" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.203859745804787</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
         <v>0</v>
@@ -41320,19 +41320,19 @@
         <v>9.9</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4496240963855421</v>
+        <v>0.6303469879518071</v>
       </c>
       <c r="J174" t="n">
-        <v>6.219799999999999</v>
+        <v>8.719799999999999</v>
       </c>
       <c r="K174" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>5.447452026313178</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
         <v>0</v>
@@ -41376,19 +41376,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>0.3968530120481927</v>
+        <v>0.5775759036144578</v>
       </c>
       <c r="J175" t="n">
-        <v>5.489799999999999</v>
+        <v>7.9898</v>
       </c>
       <c r="K175" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>7.686557122260552</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
         <v>0</v>
@@ -41397,7 +41397,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
     </row>
     <row r="176">
@@ -41432,19 +41432,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="I176" t="n">
-        <v>0.3</v>
+        <v>0.4799855421686747</v>
       </c>
       <c r="J176" t="n">
-        <v>4.15</v>
+        <v>6.639800000000001</v>
       </c>
       <c r="K176" t="n">
-        <v>2.489800000000001</v>
+        <v>0</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>9.912004008016032</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
         <v>0</v>
@@ -41488,19 +41488,19 @@
         <v>7.640000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3</v>
+        <v>0.3086602409638555</v>
       </c>
       <c r="J177" t="n">
-        <v>4.15</v>
+        <v>4.269800000000001</v>
       </c>
       <c r="K177" t="n">
-        <v>0.1198000000000006</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
         <v>0</v>
@@ -41544,25 +41544,25 @@
         <v>4.748</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>4.15</v>
+        <v>4.149999999999999</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
       </c>
       <c r="L178" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>7.202222222222223</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>0.9118000000000004</v>
+        <v>3.411799999999999</v>
       </c>
       <c r="P178" t="n">
         <v>0</v>
@@ -41609,16 +41609,16 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>4.41004</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>0.9900000000000002</v>
+        <v>3.49</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -41665,16 +41665,16 @@
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>1.623442142222222</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
         <v>0</v>
       </c>
       <c r="O180" t="n">
-        <v>0.4342000000000006</v>
+        <v>2.934200000000001</v>
       </c>
       <c r="P180" t="n">
         <v>-8.881784197001252e-16</v>
@@ -41721,7 +41721,7 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>1.458175732144</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -41730,7 +41730,7 @@
         <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>1.019824267856001</v>
+        <v>2.478000000000001</v>
       </c>
       <c r="P181" t="n">
         <v>0</v>
@@ -41768,19 +41768,19 @@
         <v>9.288</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3</v>
+        <v>0.4357734939759055</v>
       </c>
       <c r="J182" t="n">
-        <v>4.15</v>
+        <v>6.028200000000027</v>
       </c>
       <c r="K182" t="n">
-        <v>1.8782</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.670703164792736e-14</v>
       </c>
       <c r="M182" t="n">
-        <v>1.69038</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
         <v>0</v>
@@ -41824,19 +41824,19 @@
         <v>14.468</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6707132530120482</v>
+        <v>0.8514361445783132</v>
       </c>
       <c r="J183" t="n">
-        <v>9.2782</v>
+        <v>11.7782</v>
       </c>
       <c r="K183" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.93699924</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
         <v>0</v>
@@ -41880,19 +41880,19 @@
         <v>13.484</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5316144578313254</v>
+        <v>0.7123373493975905</v>
       </c>
       <c r="J184" t="n">
-        <v>7.354000000000002</v>
+        <v>9.854000000000003</v>
       </c>
       <c r="K184" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>6.17912524152</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
@@ -41901,7 +41901,7 @@
         <v>0</v>
       </c>
       <c r="P184" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -41936,19 +41936,19 @@
         <v>9.683999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3</v>
+        <v>0.4238891566265059</v>
       </c>
       <c r="J185" t="n">
-        <v>4.15</v>
+        <v>5.863799999999999</v>
       </c>
       <c r="K185" t="n">
-        <v>1.713799999999999</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>7.709186991036958</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
         <v>0</v>
@@ -42001,19 +42001,19 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>2.004</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>5.467101950388217</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
         <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>2.004000000000027</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.664535259100376e-14</v>
       </c>
     </row>
     <row r="187">
@@ -42057,16 +42057,16 @@
         <v>0</v>
       </c>
       <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
         <v>0.6818</v>
-      </c>
-      <c r="M187" t="n">
-        <v>4.698612190931885</v>
-      </c>
-      <c r="N187" t="n">
-        <v>0</v>
-      </c>
-      <c r="O187" t="n">
-        <v>0</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
@@ -42113,16 +42113,16 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
         <v>0.5080000000000005</v>
-      </c>
-      <c r="M188" t="n">
-        <v>4.124770522105576</v>
-      </c>
-      <c r="N188" t="n">
-        <v>0</v>
-      </c>
-      <c r="O188" t="n">
-        <v>0</v>
       </c>
       <c r="P188" t="n">
         <v>0</v>
@@ -42169,16 +42169,16 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
+        <v>6.661338147750939e-16</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
         <v>1.9578</v>
-      </c>
-      <c r="M189" t="n">
-        <v>1.941187647728031</v>
-      </c>
-      <c r="N189" t="n">
-        <v>0</v>
-      </c>
-      <c r="O189" t="n">
-        <v>0</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -42225,7 +42225,7 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>1.743574745189318</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
@@ -42234,7 +42234,7 @@
         <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1.938425254810682</v>
+        <v>3.682</v>
       </c>
       <c r="P190" t="n">
         <v>0</v>
@@ -42956,7 +42956,7 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.335800039999995</v>
+        <v>4.335800039999997</v>
       </c>
       <c r="N203" t="n">
         <v>9.795999999999992</v>
@@ -43174,16 +43174,16 @@
         <v>41.5</v>
       </c>
       <c r="K207" t="n">
-        <v>0.02222222222222229</v>
+        <v>0</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>10</v>
+        <v>9.980000000000006</v>
       </c>
       <c r="N207" t="n">
-        <v>22.81197777777777</v>
+        <v>22.8342</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -43230,16 +43230,16 @@
         <v>41.5</v>
       </c>
       <c r="K208" t="n">
-        <v>0.02222222222222162</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>10</v>
+        <v>9.960040000000006</v>
       </c>
       <c r="N208" t="n">
-        <v>17.93177777777777</v>
+        <v>17.95399999999999</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -43286,16 +43286,16 @@
         <v>41.5</v>
       </c>
       <c r="K209" t="n">
-        <v>0.02222222222222206</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.351659030204417</v>
       </c>
       <c r="M209" t="n">
-        <v>10</v>
+        <v>8.438276553106213</v>
       </c>
       <c r="N209" t="n">
-        <v>14.00957777777777</v>
+        <v>15.38345903020441</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -43342,7 +43342,7 @@
         <v>41.5</v>
       </c>
       <c r="K210" t="n">
-        <v>0.02222222222222118</v>
+        <v>1.754000000000001</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -43351,13 +43351,13 @@
         <v>10</v>
       </c>
       <c r="N210" t="n">
-        <v>1.731777777777784</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
     </row>
     <row r="211">
@@ -48220,7 +48220,7 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>2.250000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="N297" t="n">
         <v>4.589800000000004</v>
@@ -48270,13 +48270,13 @@
         <v>41.5</v>
       </c>
       <c r="K298" t="n">
-        <v>2.5</v>
+        <v>2.500000000000001</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>4.4955</v>
+        <v>4.495500000000002</v>
       </c>
       <c r="N298" t="n">
         <v>14.1862</v>
@@ -48332,7 +48332,7 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>6.736509</v>
+        <v>6.736509000000003</v>
       </c>
       <c r="N299" t="n">
         <v>19.99199999999999</v>
@@ -48382,13 +48382,13 @@
         <v>41.5</v>
       </c>
       <c r="K300" t="n">
-        <v>2.5</v>
+        <v>2.499999999999998</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>8.973035981999997</v>
+        <v>8.973035981999999</v>
       </c>
       <c r="N300" t="n">
         <v>13.3558</v>
@@ -48438,22 +48438,22 @@
         <v>41.5</v>
       </c>
       <c r="K301" t="n">
-        <v>0</v>
+        <v>1.16101121107111</v>
       </c>
       <c r="L301" t="n">
-        <v>1.070602963120573</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>7.765531062124251</v>
+        <v>10</v>
       </c>
       <c r="N301" t="n">
-        <v>18.36260296312058</v>
+        <v>16.13098878892889</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
       </c>
       <c r="P301" t="n">
-        <v>-3.552713678800501e-15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -48494,22 +48494,22 @@
         <v>41.5</v>
       </c>
       <c r="K302" t="n">
-        <v>2.499999999999999</v>
+        <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1.993022044088175</v>
       </c>
       <c r="M302" t="n">
-        <v>10</v>
+        <v>7.765531062124252</v>
       </c>
       <c r="N302" t="n">
-        <v>19.8762</v>
+        <v>24.36922204408817</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
       </c>
       <c r="P302" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
     </row>
     <row r="303">
@@ -48550,16 +48550,16 @@
         <v>41.5</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>2.499999999999999</v>
       </c>
       <c r="L303" t="n">
-        <v>1.993022044088177</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>7.76553106212425</v>
+        <v>10</v>
       </c>
       <c r="N303" t="n">
-        <v>25.07522204408818</v>
+        <v>20.5822</v>
       </c>
       <c r="O303" t="n">
         <v>0</v>
@@ -48606,16 +48606,16 @@
         <v>41.5</v>
       </c>
       <c r="K304" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="N304" t="n">
-        <v>20.00200000000001</v>
+        <v>22.50200000000001</v>
       </c>
       <c r="O304" t="n">
         <v>0</v>
@@ -48665,19 +48665,19 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>1.975058044088176</v>
       </c>
       <c r="M305" t="n">
-        <v>9.98</v>
+        <v>7.76553106212425</v>
       </c>
       <c r="N305" t="n">
-        <v>21.13979999999999</v>
+        <v>23.11485804408817</v>
       </c>
       <c r="O305" t="n">
         <v>0</v>
       </c>
       <c r="P305" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
     </row>
     <row r="306">
@@ -48718,16 +48718,16 @@
         <v>41.5</v>
       </c>
       <c r="K306" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>9.960040000000003</v>
+        <v>10</v>
       </c>
       <c r="N306" t="n">
-        <v>5.189999999999998</v>
+        <v>2.689999999999998</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -48780,7 +48780,7 @@
         <v>2.5</v>
       </c>
       <c r="M307" t="n">
-        <v>7.162342142222225</v>
+        <v>7.202222222222223</v>
       </c>
       <c r="N307" t="n">
         <v>0</v>
@@ -48836,7 +48836,7 @@
         <v>2.5</v>
       </c>
       <c r="M308" t="n">
-        <v>4.370239680160004</v>
+        <v>4.41004</v>
       </c>
       <c r="N308" t="n">
         <v>0</v>
@@ -48892,7 +48892,7 @@
         <v>2.5</v>
       </c>
       <c r="M309" t="n">
-        <v>1.583721423021906</v>
+        <v>1.623442142222222</v>
       </c>
       <c r="N309" t="n">
         <v>0</v>
@@ -48936,16 +48936,16 @@
         <v>8.808</v>
       </c>
       <c r="I310" t="n">
-        <v>0.5642290063254672</v>
+        <v>0.5668080774087726</v>
       </c>
       <c r="J310" t="n">
-        <v>7.805167920835631</v>
+        <v>7.840845070821355</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0.8571679208356299</v>
+        <v>0.8928450708213538</v>
       </c>
       <c r="M310" t="n">
         <v>0.6281451792473847</v>
@@ -48957,7 +48957,7 @@
         <v>0</v>
       </c>
       <c r="P310" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
     </row>
     <row r="311">
@@ -51624,19 +51624,19 @@
         <v>8.808</v>
       </c>
       <c r="I358" t="n">
-        <v>0.4518116321889651</v>
+        <v>0.5022650602409638</v>
       </c>
       <c r="J358" t="n">
-        <v>6.250060911947351</v>
+        <v>6.948</v>
       </c>
       <c r="K358" t="n">
-        <v>0.6979390880526496</v>
+        <v>0</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>0.6281451792473847</v>
+        <v>0</v>
       </c>
       <c r="N358" t="n">
         <v>0</v>
@@ -51645,7 +51645,7 @@
         <v>0</v>
       </c>
       <c r="P358" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -51689,7 +51689,7 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0.5642000000000009</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
         <v>0</v>
@@ -51698,10 +51698,10 @@
         <v>0</v>
       </c>
       <c r="O359" t="n">
-        <v>0</v>
+        <v>0.5642000000000078</v>
       </c>
       <c r="P359" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
     </row>
     <row r="360">
@@ -52968,19 +52968,19 @@
         <v>8.808</v>
       </c>
       <c r="I382" t="n">
-        <v>0.4518116321889651</v>
+        <v>0.5022650602409592</v>
       </c>
       <c r="J382" t="n">
-        <v>6.250060911947351</v>
+        <v>6.947999999999936</v>
       </c>
       <c r="K382" t="n">
-        <v>0.6979390880526496</v>
+        <v>6.525644222518975e-14</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>0.6281451792473847</v>
+        <v>5.871252913571023e-14</v>
       </c>
       <c r="N382" t="n">
         <v>0</v>
@@ -52989,7 +52989,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>-4.194175870806077e-16</v>
       </c>
     </row>
     <row r="383">
@@ -53033,7 +53033,7 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0.5642000000000009</v>
+        <v>5.273559366969493e-14</v>
       </c>
       <c r="M383" t="n">
         <v>0</v>
@@ -53042,7 +53042,7 @@
         <v>0</v>
       </c>
       <c r="O383" t="n">
-        <v>0</v>
+        <v>0.5641999999999482</v>
       </c>
       <c r="P383" t="n">
         <v>0</v>
@@ -53646,13 +53646,13 @@
         <v>41.5</v>
       </c>
       <c r="K394" t="n">
-        <v>2.5</v>
+        <v>2.499999999999999</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>2.250000000000001</v>
+        <v>2.249999999999998</v>
       </c>
       <c r="N394" t="n">
         <v>11.4342</v>
@@ -53702,13 +53702,13 @@
         <v>41.5</v>
       </c>
       <c r="K395" t="n">
-        <v>2.500000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>4.495500000000003</v>
+        <v>4.495499999999998</v>
       </c>
       <c r="N395" t="n">
         <v>18.80799999999999</v>
@@ -53758,16 +53758,16 @@
         <v>41.5</v>
       </c>
       <c r="K396" t="n">
-        <v>2.499999999999999</v>
+        <v>2.499999999999998</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
       </c>
       <c r="M396" t="n">
-        <v>6.736509000000003</v>
+        <v>6.736508999999995</v>
       </c>
       <c r="N396" t="n">
-        <v>20.3558</v>
+        <v>20.35580000000001</v>
       </c>
       <c r="O396" t="n">
         <v>0</v>
@@ -53820,7 +53820,7 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>8.973035982000003</v>
+        <v>8.973035981999994</v>
       </c>
       <c r="N397" t="n">
         <v>21.46799999999999</v>
@@ -53870,16 +53870,16 @@
         <v>41.5</v>
       </c>
       <c r="K398" t="n">
-        <v>0</v>
+        <v>1.161011211071116</v>
       </c>
       <c r="L398" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>6.177312132258224</v>
+        <v>10</v>
       </c>
       <c r="N398" t="n">
-        <v>26.8002</v>
+        <v>23.13918878892889</v>
       </c>
       <c r="O398" t="n">
         <v>0</v>
@@ -53926,16 +53926,16 @@
         <v>41.5</v>
       </c>
       <c r="K399" t="n">
-        <v>0</v>
+        <v>0.02222222222222229</v>
       </c>
       <c r="L399" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M399" t="n">
-        <v>3.38717973021593</v>
+        <v>10</v>
       </c>
       <c r="N399" t="n">
-        <v>27.4422</v>
+        <v>24.91997777777778</v>
       </c>
       <c r="O399" t="n">
         <v>0</v>
@@ -53982,16 +53982,16 @@
         <v>41.5</v>
       </c>
       <c r="K400" t="n">
-        <v>2.5</v>
+        <v>0.02222222222222162</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
       </c>
       <c r="M400" t="n">
-        <v>5.630405370755499</v>
+        <v>10</v>
       </c>
       <c r="N400" t="n">
-        <v>13.10599999999999</v>
+        <v>15.58377777777777</v>
       </c>
       <c r="O400" t="n">
         <v>0</v>
@@ -54038,16 +54038,16 @@
         <v>41.5</v>
       </c>
       <c r="K401" t="n">
-        <v>2.5</v>
+        <v>0.0222222222222214</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>7.869144560013988</v>
+        <v>10</v>
       </c>
       <c r="N401" t="n">
-        <v>5.535799999999995</v>
+        <v>8.013577777777773</v>
       </c>
       <c r="O401" t="n">
         <v>0</v>
@@ -54094,16 +54094,16 @@
         <v>41.5</v>
       </c>
       <c r="K402" t="n">
-        <v>2.385104143451157</v>
+        <v>0</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="N402" t="n">
-        <v>1.308895856548846</v>
+        <v>3.694000000000003</v>
       </c>
       <c r="O402" t="n">
         <v>0</v>
@@ -54156,7 +54156,7 @@
         <v>2.5</v>
       </c>
       <c r="M403" t="n">
-        <v>7.202222222222223</v>
+        <v>7.182262222222223</v>
       </c>
       <c r="N403" t="n">
         <v>0</v>
@@ -54212,7 +54212,7 @@
         <v>2.5</v>
       </c>
       <c r="M404" t="n">
-        <v>4.41004</v>
+        <v>4.390119920000001</v>
       </c>
       <c r="N404" t="n">
         <v>0</v>
@@ -54268,7 +54268,7 @@
         <v>2.5</v>
       </c>
       <c r="M405" t="n">
-        <v>1.623442142222222</v>
+        <v>1.603561902382223</v>
       </c>
       <c r="N405" t="n">
         <v>0</v>
@@ -54312,16 +54312,16 @@
         <v>9.884</v>
       </c>
       <c r="I406" t="n">
-        <v>0.6854584866610121</v>
+        <v>0.6841676602929914</v>
       </c>
       <c r="J406" t="n">
-        <v>9.482175732144</v>
+        <v>9.464319300719714</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>1.458175732144</v>
+        <v>1.440319300719713</v>
       </c>
       <c r="M406" t="n">
         <v>0</v>
@@ -59084,7 +59084,7 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>3.401672039999997</v>
+        <v>3.401672039999989</v>
       </c>
       <c r="N491" t="n">
         <v>4.828000000000003</v>
@@ -59140,7 +59140,7 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>5.644868695919998</v>
+        <v>5.644868695919989</v>
       </c>
       <c r="N492" t="n">
         <v>10.3998</v>
@@ -59196,7 +59196,7 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>7.883578958528158</v>
+        <v>7.883578958528149</v>
       </c>
       <c r="N493" t="n">
         <v>13.2</v>
@@ -62936,19 +62936,19 @@
         <v>10.744</v>
       </c>
       <c r="I560" t="n">
-        <v>0.4464891544035745</v>
+        <v>0.5959373493975904</v>
       </c>
       <c r="J560" t="n">
-        <v>6.17643330258278</v>
+        <v>8.2438</v>
       </c>
       <c r="K560" t="n">
-        <v>2.06736669741722</v>
+        <v>0</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>1.860630027675498</v>
+        <v>0</v>
       </c>
       <c r="N560" t="n">
         <v>0</v>
@@ -62992,19 +62992,19 @@
         <v>10.34</v>
       </c>
       <c r="I561" t="n">
-        <v>0.3231180722891566</v>
+        <v>0.5038409638554217</v>
       </c>
       <c r="J561" t="n">
-        <v>4.4698</v>
+        <v>6.9698</v>
       </c>
       <c r="K561" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>4.106908767620147</v>
+        <v>0</v>
       </c>
       <c r="N561" t="n">
         <v>0</v>
@@ -63048,19 +63048,19 @@
         <v>9.671999999999999</v>
       </c>
       <c r="I562" t="n">
-        <v>0.3</v>
+        <v>0.4093156626506023</v>
       </c>
       <c r="J562" t="n">
-        <v>4.15</v>
+        <v>5.662199999999999</v>
       </c>
       <c r="K562" t="n">
-        <v>1.512199999999998</v>
+        <v>0</v>
       </c>
       <c r="L562" t="n">
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>5.459674950084906</v>
+        <v>0</v>
       </c>
       <c r="N562" t="n">
         <v>0</v>
@@ -63113,16 +63113,16 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>1.402</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="M563" t="n">
-        <v>3.890977822406958</v>
+        <v>0</v>
       </c>
       <c r="N563" t="n">
         <v>0</v>
       </c>
       <c r="O563" t="n">
-        <v>0</v>
+        <v>1.401999999999999</v>
       </c>
       <c r="P563" t="n">
         <v>0</v>
@@ -63169,19 +63169,19 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>2.2302</v>
+        <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>1.405195866762145</v>
+        <v>0</v>
       </c>
       <c r="N564" t="n">
         <v>0</v>
       </c>
       <c r="O564" t="n">
-        <v>0</v>
+        <v>2.230200000000002</v>
       </c>
       <c r="P564" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
     </row>
     <row r="565">
@@ -63225,19 +63225,19 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0.7100000000000009</v>
+        <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>0.6134965861397307</v>
+        <v>0</v>
       </c>
       <c r="N565" t="n">
         <v>0</v>
       </c>
       <c r="O565" t="n">
-        <v>0</v>
+        <v>0.7100000000000023</v>
       </c>
       <c r="P565" t="n">
-        <v>0</v>
+        <v>1.77635683940025e-15</v>
       </c>
     </row>
     <row r="566">
@@ -63284,7 +63284,7 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>0.6122695929674512</v>
+        <v>0</v>
       </c>
       <c r="N566" t="n">
         <v>0</v>
@@ -63340,7 +63340,7 @@
         <v>0</v>
       </c>
       <c r="M567" t="n">
-        <v>0.6110450537815164</v>
+        <v>0</v>
       </c>
       <c r="N567" t="n">
         <v>0</v>
@@ -63384,19 +63384,19 @@
         <v>10.552</v>
       </c>
       <c r="I568" t="n">
-        <v>0.3196626506024096</v>
+        <v>0.5003855421686747</v>
       </c>
       <c r="J568" t="n">
-        <v>4.422</v>
+        <v>6.922000000000001</v>
       </c>
       <c r="K568" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L568" t="n">
         <v>0</v>
       </c>
       <c r="M568" t="n">
-        <v>2.859822963673953</v>
+        <v>0</v>
       </c>
       <c r="N568" t="n">
         <v>0</v>
@@ -63405,7 +63405,7 @@
         <v>0</v>
       </c>
       <c r="P568" t="n">
-        <v>0</v>
+        <v>-8.881784197001252e-16</v>
       </c>
     </row>
     <row r="569">
@@ -63449,19 +63449,19 @@
         <v>0</v>
       </c>
       <c r="L569" t="n">
-        <v>1.3222</v>
+        <v>0</v>
       </c>
       <c r="M569" t="n">
-        <v>1.384992206635494</v>
+        <v>0</v>
       </c>
       <c r="N569" t="n">
         <v>0</v>
       </c>
       <c r="O569" t="n">
-        <v>0</v>
+        <v>1.322200000000007</v>
       </c>
       <c r="P569" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
     </row>
     <row r="570">
@@ -63505,7 +63505,7 @@
         <v>0</v>
       </c>
       <c r="L570" t="n">
-        <v>1.244000000000001</v>
+        <v>1.998401444325282e-15</v>
       </c>
       <c r="M570" t="n">
         <v>0</v>
@@ -63514,7 +63514,7 @@
         <v>0</v>
       </c>
       <c r="O570" t="n">
-        <v>0</v>
+        <v>1.243999999999999</v>
       </c>
       <c r="P570" t="n">
         <v>0</v>
